--- a/tests/fixtures/consistency/DD02_画面設計書_SCR002_受注登録.xlsx
+++ b/tests/fixtures/consistency/DD02_画面設計書_SCR002_受注登録.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面レイアウト" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面項目定義" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="イベント定義" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表示制御" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6806,4 +6807,2191 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BF29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
+  <cols>
+    <col width="2.75" customWidth="1" min="1" max="1"/>
+    <col width="2.75" customWidth="1" min="2" max="2"/>
+    <col width="2.75" customWidth="1" min="3" max="3"/>
+    <col width="2.75" customWidth="1" min="4" max="4"/>
+    <col width="2.75" customWidth="1" min="5" max="5"/>
+    <col width="2.75" customWidth="1" min="6" max="6"/>
+    <col width="2.75" customWidth="1" min="7" max="7"/>
+    <col width="2.75" customWidth="1" min="8" max="8"/>
+    <col width="2.75" customWidth="1" min="9" max="9"/>
+    <col width="2.75" customWidth="1" min="10" max="10"/>
+    <col width="2.75" customWidth="1" min="11" max="11"/>
+    <col width="2.75" customWidth="1" min="12" max="12"/>
+    <col width="2.75" customWidth="1" min="13" max="13"/>
+    <col width="2.75" customWidth="1" min="14" max="14"/>
+    <col width="2.75" customWidth="1" min="15" max="15"/>
+    <col width="2.75" customWidth="1" min="16" max="16"/>
+    <col width="2.75" customWidth="1" min="17" max="17"/>
+    <col width="2.75" customWidth="1" min="18" max="18"/>
+    <col width="2.75" customWidth="1" min="19" max="19"/>
+    <col width="2.75" customWidth="1" min="20" max="20"/>
+    <col width="2.75" customWidth="1" min="21" max="21"/>
+    <col width="2.75" customWidth="1" min="22" max="22"/>
+    <col width="2.75" customWidth="1" min="23" max="23"/>
+    <col width="2.75" customWidth="1" min="24" max="24"/>
+    <col width="2.75" customWidth="1" min="25" max="25"/>
+    <col width="2.75" customWidth="1" min="26" max="26"/>
+    <col width="2.75" customWidth="1" min="27" max="27"/>
+    <col width="2.75" customWidth="1" min="28" max="28"/>
+    <col width="2.75" customWidth="1" min="29" max="29"/>
+    <col width="2.75" customWidth="1" min="30" max="30"/>
+    <col width="2.75" customWidth="1" min="31" max="31"/>
+    <col width="2.75" customWidth="1" min="32" max="32"/>
+    <col width="2.75" customWidth="1" min="33" max="33"/>
+    <col width="2.75" customWidth="1" min="34" max="34"/>
+    <col width="2.75" customWidth="1" min="35" max="35"/>
+    <col width="2.75" customWidth="1" min="36" max="36"/>
+    <col width="2.75" customWidth="1" min="37" max="37"/>
+    <col width="2.75" customWidth="1" min="38" max="38"/>
+    <col width="2.75" customWidth="1" min="39" max="39"/>
+    <col width="2.75" customWidth="1" min="40" max="40"/>
+    <col width="2.75" customWidth="1" min="41" max="41"/>
+    <col width="2.75" customWidth="1" min="42" max="42"/>
+    <col width="2.75" customWidth="1" min="43" max="43"/>
+    <col width="2.75" customWidth="1" min="44" max="44"/>
+    <col width="2.75" customWidth="1" min="45" max="45"/>
+    <col width="2.75" customWidth="1" min="46" max="46"/>
+    <col width="2.75" customWidth="1" min="47" max="47"/>
+    <col width="2.75" customWidth="1" min="48" max="48"/>
+    <col width="2.75" customWidth="1" min="49" max="49"/>
+    <col width="2.75" customWidth="1" min="50" max="50"/>
+    <col width="2.75" customWidth="1" min="51" max="51"/>
+    <col width="2.75" customWidth="1" min="52" max="52"/>
+    <col width="2.75" customWidth="1" min="53" max="53"/>
+    <col width="2.75" customWidth="1" min="54" max="54"/>
+    <col width="2.75" customWidth="1" min="55" max="55"/>
+    <col width="2.75" customWidth="1" min="56" max="56"/>
+    <col width="2.75" customWidth="1" min="57" max="57"/>
+    <col width="2.75" customWidth="1" min="58" max="58"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>画面設計書</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="n"/>
+      <c r="C1" s="31" t="n"/>
+      <c r="D1" s="31" t="n"/>
+      <c r="E1" s="31" t="n"/>
+      <c r="F1" s="31" t="n"/>
+      <c r="G1" s="31" t="n"/>
+      <c r="H1" s="31" t="n"/>
+      <c r="I1" s="31" t="n"/>
+      <c r="J1" s="31" t="n"/>
+      <c r="K1" s="31" t="n"/>
+      <c r="L1" s="31" t="n"/>
+      <c r="M1" s="31" t="n"/>
+      <c r="N1" s="32" t="n"/>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>システム名</t>
+        </is>
+      </c>
+      <c r="P1" s="28" t="n"/>
+      <c r="Q1" s="28" t="n"/>
+      <c r="R1" s="29" t="n"/>
+      <c r="S1" s="6" t="inlineStr">
+        <is>
+          <t>受注管理システム</t>
+        </is>
+      </c>
+      <c r="T1" s="28" t="n"/>
+      <c r="U1" s="28" t="n"/>
+      <c r="V1" s="28" t="n"/>
+      <c r="W1" s="28" t="n"/>
+      <c r="X1" s="28" t="n"/>
+      <c r="Y1" s="28" t="n"/>
+      <c r="Z1" s="28" t="n"/>
+      <c r="AA1" s="28" t="n"/>
+      <c r="AB1" s="28" t="n"/>
+      <c r="AC1" s="28" t="n"/>
+      <c r="AD1" s="28" t="n"/>
+      <c r="AE1" s="28" t="n"/>
+      <c r="AF1" s="28" t="n"/>
+      <c r="AG1" s="28" t="n"/>
+      <c r="AH1" s="29" t="n"/>
+      <c r="AI1" s="4" t="inlineStr">
+        <is>
+          <t>作成者</t>
+        </is>
+      </c>
+      <c r="AJ1" s="28" t="n"/>
+      <c r="AK1" s="28" t="n"/>
+      <c r="AL1" s="29" t="n"/>
+      <c r="AM1" s="6" t="inlineStr">
+        <is>
+          <t>山田 太郎</t>
+        </is>
+      </c>
+      <c r="AN1" s="28" t="n"/>
+      <c r="AO1" s="28" t="n"/>
+      <c r="AP1" s="28" t="n"/>
+      <c r="AQ1" s="28" t="n"/>
+      <c r="AR1" s="28" t="n"/>
+      <c r="AS1" s="28" t="n"/>
+      <c r="AT1" s="29" t="n"/>
+      <c r="AU1" s="4" t="inlineStr">
+        <is>
+          <t>作成日</t>
+        </is>
+      </c>
+      <c r="AV1" s="28" t="n"/>
+      <c r="AW1" s="28" t="n"/>
+      <c r="AX1" s="29" t="n"/>
+      <c r="AY1" s="30" t="n">
+        <v>46296</v>
+      </c>
+      <c r="AZ1" s="28" t="n"/>
+      <c r="BA1" s="28" t="n"/>
+      <c r="BB1" s="28" t="n"/>
+      <c r="BC1" s="28" t="n"/>
+      <c r="BD1" s="28" t="n"/>
+      <c r="BE1" s="28" t="n"/>
+      <c r="BF1" s="29" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="33" t="n"/>
+      <c r="B2" s="34" t="n"/>
+      <c r="C2" s="34" t="n"/>
+      <c r="D2" s="34" t="n"/>
+      <c r="E2" s="34" t="n"/>
+      <c r="F2" s="34" t="n"/>
+      <c r="G2" s="34" t="n"/>
+      <c r="H2" s="34" t="n"/>
+      <c r="I2" s="34" t="n"/>
+      <c r="J2" s="34" t="n"/>
+      <c r="K2" s="34" t="n"/>
+      <c r="L2" s="34" t="n"/>
+      <c r="M2" s="34" t="n"/>
+      <c r="N2" s="35" t="n"/>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>画面ID</t>
+        </is>
+      </c>
+      <c r="P2" s="28" t="n"/>
+      <c r="Q2" s="28" t="n"/>
+      <c r="R2" s="29" t="n"/>
+      <c r="S2" s="6" t="inlineStr">
+        <is>
+          <t>SCR002</t>
+        </is>
+      </c>
+      <c r="T2" s="28" t="n"/>
+      <c r="U2" s="28" t="n"/>
+      <c r="V2" s="28" t="n"/>
+      <c r="W2" s="28" t="n"/>
+      <c r="X2" s="29" t="n"/>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>画面名</t>
+        </is>
+      </c>
+      <c r="Z2" s="28" t="n"/>
+      <c r="AA2" s="28" t="n"/>
+      <c r="AB2" s="29" t="n"/>
+      <c r="AC2" s="6" t="inlineStr">
+        <is>
+          <t>受注登録</t>
+        </is>
+      </c>
+      <c r="AD2" s="28" t="n"/>
+      <c r="AE2" s="28" t="n"/>
+      <c r="AF2" s="28" t="n"/>
+      <c r="AG2" s="28" t="n"/>
+      <c r="AH2" s="29" t="n"/>
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t>更新者</t>
+        </is>
+      </c>
+      <c r="AJ2" s="28" t="n"/>
+      <c r="AK2" s="28" t="n"/>
+      <c r="AL2" s="29" t="n"/>
+      <c r="AM2" s="6" t="inlineStr">
+        <is>
+          <t>山田 太郎</t>
+        </is>
+      </c>
+      <c r="AN2" s="28" t="n"/>
+      <c r="AO2" s="28" t="n"/>
+      <c r="AP2" s="28" t="n"/>
+      <c r="AQ2" s="28" t="n"/>
+      <c r="AR2" s="28" t="n"/>
+      <c r="AS2" s="28" t="n"/>
+      <c r="AT2" s="29" t="n"/>
+      <c r="AU2" s="4" t="inlineStr">
+        <is>
+          <t>更新日</t>
+        </is>
+      </c>
+      <c r="AV2" s="28" t="n"/>
+      <c r="AW2" s="28" t="n"/>
+      <c r="AX2" s="29" t="n"/>
+      <c r="AY2" s="30" t="n">
+        <v>46296</v>
+      </c>
+      <c r="AZ2" s="28" t="n"/>
+      <c r="BA2" s="28" t="n"/>
+      <c r="BB2" s="28" t="n"/>
+      <c r="BC2" s="28" t="n"/>
+      <c r="BD2" s="28" t="n"/>
+      <c r="BE2" s="28" t="n"/>
+      <c r="BF2" s="29" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>■ 状態（イベントは、その状態になるイベント）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="28" t="n"/>
+      <c r="G5" s="28" t="n"/>
+      <c r="H5" s="28" t="n"/>
+      <c r="I5" s="28" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>条件</t>
+        </is>
+      </c>
+      <c r="L5" s="28" t="n"/>
+      <c r="M5" s="28" t="n"/>
+      <c r="N5" s="28" t="n"/>
+      <c r="O5" s="28" t="n"/>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="28" t="n"/>
+      <c r="R5" s="28" t="n"/>
+      <c r="S5" s="28" t="n"/>
+      <c r="T5" s="28" t="n"/>
+      <c r="U5" s="28" t="n"/>
+      <c r="V5" s="28" t="n"/>
+      <c r="W5" s="28" t="n"/>
+      <c r="X5" s="28" t="n"/>
+      <c r="Y5" s="28" t="n"/>
+      <c r="Z5" s="28" t="n"/>
+      <c r="AA5" s="28" t="n"/>
+      <c r="AB5" s="28" t="n"/>
+      <c r="AC5" s="28" t="n"/>
+      <c r="AD5" s="28" t="n"/>
+      <c r="AE5" s="28" t="n"/>
+      <c r="AF5" s="28" t="n"/>
+      <c r="AG5" s="28" t="n"/>
+      <c r="AH5" s="28" t="n"/>
+      <c r="AI5" s="28" t="n"/>
+      <c r="AJ5" s="28" t="n"/>
+      <c r="AK5" s="28" t="n"/>
+      <c r="AL5" s="28" t="n"/>
+      <c r="AM5" s="28" t="n"/>
+      <c r="AN5" s="29" t="n"/>
+      <c r="AO5" s="12" t="inlineStr">
+        <is>
+          <t>イベント</t>
+        </is>
+      </c>
+      <c r="AP5" s="28" t="n"/>
+      <c r="AQ5" s="28" t="n"/>
+      <c r="AR5" s="28" t="n"/>
+      <c r="AS5" s="28" t="n"/>
+      <c r="AT5" s="28" t="n"/>
+      <c r="AU5" s="28" t="n"/>
+      <c r="AV5" s="28" t="n"/>
+      <c r="AW5" s="28" t="n"/>
+      <c r="AX5" s="29" t="n"/>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="29" t="n"/>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>入力中</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="n"/>
+      <c r="E6" s="28" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
+      <c r="H6" s="28" t="n"/>
+      <c r="I6" s="28" t="n"/>
+      <c r="J6" s="29" t="n"/>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>明細が20行未満のとき</t>
+        </is>
+      </c>
+      <c r="L6" s="28" t="n"/>
+      <c r="M6" s="28" t="n"/>
+      <c r="N6" s="28" t="n"/>
+      <c r="O6" s="28" t="n"/>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="28" t="n"/>
+      <c r="R6" s="28" t="n"/>
+      <c r="S6" s="28" t="n"/>
+      <c r="T6" s="28" t="n"/>
+      <c r="U6" s="28" t="n"/>
+      <c r="V6" s="28" t="n"/>
+      <c r="W6" s="28" t="n"/>
+      <c r="X6" s="28" t="n"/>
+      <c r="Y6" s="28" t="n"/>
+      <c r="Z6" s="28" t="n"/>
+      <c r="AA6" s="28" t="n"/>
+      <c r="AB6" s="28" t="n"/>
+      <c r="AC6" s="28" t="n"/>
+      <c r="AD6" s="28" t="n"/>
+      <c r="AE6" s="28" t="n"/>
+      <c r="AF6" s="28" t="n"/>
+      <c r="AG6" s="28" t="n"/>
+      <c r="AH6" s="28" t="n"/>
+      <c r="AI6" s="28" t="n"/>
+      <c r="AJ6" s="28" t="n"/>
+      <c r="AK6" s="28" t="n"/>
+      <c r="AL6" s="28" t="n"/>
+      <c r="AM6" s="28" t="n"/>
+      <c r="AN6" s="29" t="n"/>
+      <c r="AO6" s="14" t="inlineStr">
+        <is>
+          <t>EV01、EV05</t>
+        </is>
+      </c>
+      <c r="AP6" s="28" t="n"/>
+      <c r="AQ6" s="28" t="n"/>
+      <c r="AR6" s="28" t="n"/>
+      <c r="AS6" s="28" t="n"/>
+      <c r="AT6" s="28" t="n"/>
+      <c r="AU6" s="28" t="n"/>
+      <c r="AV6" s="28" t="n"/>
+      <c r="AW6" s="28" t="n"/>
+      <c r="AX6" s="29" t="n"/>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>明細20行</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
+      <c r="H7" s="28" t="n"/>
+      <c r="I7" s="28" t="n"/>
+      <c r="J7" s="29" t="n"/>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>明細が20行になったとき</t>
+        </is>
+      </c>
+      <c r="L7" s="28" t="n"/>
+      <c r="M7" s="28" t="n"/>
+      <c r="N7" s="28" t="n"/>
+      <c r="O7" s="28" t="n"/>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="28" t="n"/>
+      <c r="R7" s="28" t="n"/>
+      <c r="S7" s="28" t="n"/>
+      <c r="T7" s="28" t="n"/>
+      <c r="U7" s="28" t="n"/>
+      <c r="V7" s="28" t="n"/>
+      <c r="W7" s="28" t="n"/>
+      <c r="X7" s="28" t="n"/>
+      <c r="Y7" s="28" t="n"/>
+      <c r="Z7" s="28" t="n"/>
+      <c r="AA7" s="28" t="n"/>
+      <c r="AB7" s="28" t="n"/>
+      <c r="AC7" s="28" t="n"/>
+      <c r="AD7" s="28" t="n"/>
+      <c r="AE7" s="28" t="n"/>
+      <c r="AF7" s="28" t="n"/>
+      <c r="AG7" s="28" t="n"/>
+      <c r="AH7" s="28" t="n"/>
+      <c r="AI7" s="28" t="n"/>
+      <c r="AJ7" s="28" t="n"/>
+      <c r="AK7" s="28" t="n"/>
+      <c r="AL7" s="28" t="n"/>
+      <c r="AM7" s="28" t="n"/>
+      <c r="AN7" s="29" t="n"/>
+      <c r="AO7" s="14" t="inlineStr">
+        <is>
+          <t>EV05</t>
+        </is>
+      </c>
+      <c r="AP7" s="28" t="n"/>
+      <c r="AQ7" s="28" t="n"/>
+      <c r="AR7" s="28" t="n"/>
+      <c r="AS7" s="28" t="n"/>
+      <c r="AT7" s="28" t="n"/>
+      <c r="AU7" s="28" t="n"/>
+      <c r="AV7" s="28" t="n"/>
+      <c r="AW7" s="28" t="n"/>
+      <c r="AX7" s="29" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>■ 項目の表示制御（○:表示 △:非活性 ×:非表示 表示のみ:表示するが変更できない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="n"/>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>項目名</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="n"/>
+      <c r="E10" s="28" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
+      <c r="H10" s="28" t="n"/>
+      <c r="I10" s="29" t="n"/>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>項目ID</t>
+        </is>
+      </c>
+      <c r="K10" s="28" t="n"/>
+      <c r="L10" s="28" t="n"/>
+      <c r="M10" s="28" t="n"/>
+      <c r="N10" s="28" t="n"/>
+      <c r="O10" s="28" t="n"/>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="29" t="n"/>
+      <c r="R10" s="12" t="inlineStr">
+        <is>
+          <t>入力中</t>
+        </is>
+      </c>
+      <c r="S10" s="28" t="n"/>
+      <c r="T10" s="28" t="n"/>
+      <c r="U10" s="28" t="n"/>
+      <c r="V10" s="29" t="n"/>
+      <c r="W10" s="12" t="inlineStr">
+        <is>
+          <t>明細20行</t>
+        </is>
+      </c>
+      <c r="X10" s="28" t="n"/>
+      <c r="Y10" s="28" t="n"/>
+      <c r="Z10" s="28" t="n"/>
+      <c r="AA10" s="29" t="n"/>
+      <c r="AB10" s="12" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="AC10" s="28" t="n"/>
+      <c r="AD10" s="28" t="n"/>
+      <c r="AE10" s="28" t="n"/>
+      <c r="AF10" s="28" t="n"/>
+      <c r="AG10" s="28" t="n"/>
+      <c r="AH10" s="28" t="n"/>
+      <c r="AI10" s="28" t="n"/>
+      <c r="AJ10" s="28" t="n"/>
+      <c r="AK10" s="28" t="n"/>
+      <c r="AL10" s="28" t="n"/>
+      <c r="AM10" s="28" t="n"/>
+      <c r="AN10" s="28" t="n"/>
+      <c r="AO10" s="28" t="n"/>
+      <c r="AP10" s="28" t="n"/>
+      <c r="AQ10" s="28" t="n"/>
+      <c r="AR10" s="28" t="n"/>
+      <c r="AS10" s="28" t="n"/>
+      <c r="AT10" s="28" t="n"/>
+      <c r="AU10" s="28" t="n"/>
+      <c r="AV10" s="28" t="n"/>
+      <c r="AW10" s="28" t="n"/>
+      <c r="AX10" s="28" t="n"/>
+      <c r="AY10" s="28" t="n"/>
+      <c r="AZ10" s="28" t="n"/>
+      <c r="BA10" s="28" t="n"/>
+      <c r="BB10" s="28" t="n"/>
+      <c r="BC10" s="28" t="n"/>
+      <c r="BD10" s="28" t="n"/>
+      <c r="BE10" s="28" t="n"/>
+      <c r="BF10" s="29" t="n"/>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>受注日</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
+      <c r="H11" s="28" t="n"/>
+      <c r="I11" s="29" t="n"/>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>orderDate</t>
+        </is>
+      </c>
+      <c r="K11" s="28" t="n"/>
+      <c r="L11" s="28" t="n"/>
+      <c r="M11" s="28" t="n"/>
+      <c r="N11" s="28" t="n"/>
+      <c r="O11" s="28" t="n"/>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="29" t="n"/>
+      <c r="R11" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S11" s="28" t="n"/>
+      <c r="T11" s="28" t="n"/>
+      <c r="U11" s="28" t="n"/>
+      <c r="V11" s="29" t="n"/>
+      <c r="W11" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X11" s="28" t="n"/>
+      <c r="Y11" s="28" t="n"/>
+      <c r="Z11" s="28" t="n"/>
+      <c r="AA11" s="29" t="n"/>
+      <c r="AB11" s="14" t="inlineStr"/>
+      <c r="AC11" s="28" t="n"/>
+      <c r="AD11" s="28" t="n"/>
+      <c r="AE11" s="28" t="n"/>
+      <c r="AF11" s="28" t="n"/>
+      <c r="AG11" s="28" t="n"/>
+      <c r="AH11" s="28" t="n"/>
+      <c r="AI11" s="28" t="n"/>
+      <c r="AJ11" s="28" t="n"/>
+      <c r="AK11" s="28" t="n"/>
+      <c r="AL11" s="28" t="n"/>
+      <c r="AM11" s="28" t="n"/>
+      <c r="AN11" s="28" t="n"/>
+      <c r="AO11" s="28" t="n"/>
+      <c r="AP11" s="28" t="n"/>
+      <c r="AQ11" s="28" t="n"/>
+      <c r="AR11" s="28" t="n"/>
+      <c r="AS11" s="28" t="n"/>
+      <c r="AT11" s="28" t="n"/>
+      <c r="AU11" s="28" t="n"/>
+      <c r="AV11" s="28" t="n"/>
+      <c r="AW11" s="28" t="n"/>
+      <c r="AX11" s="28" t="n"/>
+      <c r="AY11" s="28" t="n"/>
+      <c r="AZ11" s="28" t="n"/>
+      <c r="BA11" s="28" t="n"/>
+      <c r="BB11" s="28" t="n"/>
+      <c r="BC11" s="28" t="n"/>
+      <c r="BD11" s="28" t="n"/>
+      <c r="BE11" s="28" t="n"/>
+      <c r="BF11" s="29" t="n"/>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="29" t="n"/>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>顧客コード</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
+      <c r="H12" s="28" t="n"/>
+      <c r="I12" s="29" t="n"/>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>customerCd</t>
+        </is>
+      </c>
+      <c r="K12" s="28" t="n"/>
+      <c r="L12" s="28" t="n"/>
+      <c r="M12" s="28" t="n"/>
+      <c r="N12" s="28" t="n"/>
+      <c r="O12" s="28" t="n"/>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="29" t="n"/>
+      <c r="R12" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S12" s="28" t="n"/>
+      <c r="T12" s="28" t="n"/>
+      <c r="U12" s="28" t="n"/>
+      <c r="V12" s="29" t="n"/>
+      <c r="W12" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X12" s="28" t="n"/>
+      <c r="Y12" s="28" t="n"/>
+      <c r="Z12" s="28" t="n"/>
+      <c r="AA12" s="29" t="n"/>
+      <c r="AB12" s="14" t="inlineStr"/>
+      <c r="AC12" s="28" t="n"/>
+      <c r="AD12" s="28" t="n"/>
+      <c r="AE12" s="28" t="n"/>
+      <c r="AF12" s="28" t="n"/>
+      <c r="AG12" s="28" t="n"/>
+      <c r="AH12" s="28" t="n"/>
+      <c r="AI12" s="28" t="n"/>
+      <c r="AJ12" s="28" t="n"/>
+      <c r="AK12" s="28" t="n"/>
+      <c r="AL12" s="28" t="n"/>
+      <c r="AM12" s="28" t="n"/>
+      <c r="AN12" s="28" t="n"/>
+      <c r="AO12" s="28" t="n"/>
+      <c r="AP12" s="28" t="n"/>
+      <c r="AQ12" s="28" t="n"/>
+      <c r="AR12" s="28" t="n"/>
+      <c r="AS12" s="28" t="n"/>
+      <c r="AT12" s="28" t="n"/>
+      <c r="AU12" s="28" t="n"/>
+      <c r="AV12" s="28" t="n"/>
+      <c r="AW12" s="28" t="n"/>
+      <c r="AX12" s="28" t="n"/>
+      <c r="AY12" s="28" t="n"/>
+      <c r="AZ12" s="28" t="n"/>
+      <c r="BA12" s="28" t="n"/>
+      <c r="BB12" s="28" t="n"/>
+      <c r="BC12" s="28" t="n"/>
+      <c r="BD12" s="28" t="n"/>
+      <c r="BE12" s="28" t="n"/>
+      <c r="BF12" s="29" t="n"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="29" t="n"/>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>顧客名</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="n"/>
+      <c r="E13" s="28" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
+      <c r="H13" s="28" t="n"/>
+      <c r="I13" s="29" t="n"/>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>customerName</t>
+        </is>
+      </c>
+      <c r="K13" s="28" t="n"/>
+      <c r="L13" s="28" t="n"/>
+      <c r="M13" s="28" t="n"/>
+      <c r="N13" s="28" t="n"/>
+      <c r="O13" s="28" t="n"/>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="29" t="n"/>
+      <c r="R13" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S13" s="28" t="n"/>
+      <c r="T13" s="28" t="n"/>
+      <c r="U13" s="28" t="n"/>
+      <c r="V13" s="29" t="n"/>
+      <c r="W13" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X13" s="28" t="n"/>
+      <c r="Y13" s="28" t="n"/>
+      <c r="Z13" s="28" t="n"/>
+      <c r="AA13" s="29" t="n"/>
+      <c r="AB13" s="14" t="inlineStr"/>
+      <c r="AC13" s="28" t="n"/>
+      <c r="AD13" s="28" t="n"/>
+      <c r="AE13" s="28" t="n"/>
+      <c r="AF13" s="28" t="n"/>
+      <c r="AG13" s="28" t="n"/>
+      <c r="AH13" s="28" t="n"/>
+      <c r="AI13" s="28" t="n"/>
+      <c r="AJ13" s="28" t="n"/>
+      <c r="AK13" s="28" t="n"/>
+      <c r="AL13" s="28" t="n"/>
+      <c r="AM13" s="28" t="n"/>
+      <c r="AN13" s="28" t="n"/>
+      <c r="AO13" s="28" t="n"/>
+      <c r="AP13" s="28" t="n"/>
+      <c r="AQ13" s="28" t="n"/>
+      <c r="AR13" s="28" t="n"/>
+      <c r="AS13" s="28" t="n"/>
+      <c r="AT13" s="28" t="n"/>
+      <c r="AU13" s="28" t="n"/>
+      <c r="AV13" s="28" t="n"/>
+      <c r="AW13" s="28" t="n"/>
+      <c r="AX13" s="28" t="n"/>
+      <c r="AY13" s="28" t="n"/>
+      <c r="AZ13" s="28" t="n"/>
+      <c r="BA13" s="28" t="n"/>
+      <c r="BB13" s="28" t="n"/>
+      <c r="BC13" s="28" t="n"/>
+      <c r="BD13" s="28" t="n"/>
+      <c r="BE13" s="28" t="n"/>
+      <c r="BF13" s="29" t="n"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="29" t="n"/>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>支払方法</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
+      <c r="H14" s="28" t="n"/>
+      <c r="I14" s="29" t="n"/>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>paymentMethod</t>
+        </is>
+      </c>
+      <c r="K14" s="28" t="n"/>
+      <c r="L14" s="28" t="n"/>
+      <c r="M14" s="28" t="n"/>
+      <c r="N14" s="28" t="n"/>
+      <c r="O14" s="28" t="n"/>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="29" t="n"/>
+      <c r="R14" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S14" s="28" t="n"/>
+      <c r="T14" s="28" t="n"/>
+      <c r="U14" s="28" t="n"/>
+      <c r="V14" s="29" t="n"/>
+      <c r="W14" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X14" s="28" t="n"/>
+      <c r="Y14" s="28" t="n"/>
+      <c r="Z14" s="28" t="n"/>
+      <c r="AA14" s="29" t="n"/>
+      <c r="AB14" s="14" t="inlineStr"/>
+      <c r="AC14" s="28" t="n"/>
+      <c r="AD14" s="28" t="n"/>
+      <c r="AE14" s="28" t="n"/>
+      <c r="AF14" s="28" t="n"/>
+      <c r="AG14" s="28" t="n"/>
+      <c r="AH14" s="28" t="n"/>
+      <c r="AI14" s="28" t="n"/>
+      <c r="AJ14" s="28" t="n"/>
+      <c r="AK14" s="28" t="n"/>
+      <c r="AL14" s="28" t="n"/>
+      <c r="AM14" s="28" t="n"/>
+      <c r="AN14" s="28" t="n"/>
+      <c r="AO14" s="28" t="n"/>
+      <c r="AP14" s="28" t="n"/>
+      <c r="AQ14" s="28" t="n"/>
+      <c r="AR14" s="28" t="n"/>
+      <c r="AS14" s="28" t="n"/>
+      <c r="AT14" s="28" t="n"/>
+      <c r="AU14" s="28" t="n"/>
+      <c r="AV14" s="28" t="n"/>
+      <c r="AW14" s="28" t="n"/>
+      <c r="AX14" s="28" t="n"/>
+      <c r="AY14" s="28" t="n"/>
+      <c r="AZ14" s="28" t="n"/>
+      <c r="BA14" s="28" t="n"/>
+      <c r="BB14" s="28" t="n"/>
+      <c r="BC14" s="28" t="n"/>
+      <c r="BD14" s="28" t="n"/>
+      <c r="BE14" s="28" t="n"/>
+      <c r="BF14" s="29" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="29" t="n"/>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>希望納品日</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="n"/>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="29" t="n"/>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>deliveryDate</t>
+        </is>
+      </c>
+      <c r="K15" s="28" t="n"/>
+      <c r="L15" s="28" t="n"/>
+      <c r="M15" s="28" t="n"/>
+      <c r="N15" s="28" t="n"/>
+      <c r="O15" s="28" t="n"/>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="29" t="n"/>
+      <c r="R15" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S15" s="28" t="n"/>
+      <c r="T15" s="28" t="n"/>
+      <c r="U15" s="28" t="n"/>
+      <c r="V15" s="29" t="n"/>
+      <c r="W15" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X15" s="28" t="n"/>
+      <c r="Y15" s="28" t="n"/>
+      <c r="Z15" s="28" t="n"/>
+      <c r="AA15" s="29" t="n"/>
+      <c r="AB15" s="14" t="inlineStr"/>
+      <c r="AC15" s="28" t="n"/>
+      <c r="AD15" s="28" t="n"/>
+      <c r="AE15" s="28" t="n"/>
+      <c r="AF15" s="28" t="n"/>
+      <c r="AG15" s="28" t="n"/>
+      <c r="AH15" s="28" t="n"/>
+      <c r="AI15" s="28" t="n"/>
+      <c r="AJ15" s="28" t="n"/>
+      <c r="AK15" s="28" t="n"/>
+      <c r="AL15" s="28" t="n"/>
+      <c r="AM15" s="28" t="n"/>
+      <c r="AN15" s="28" t="n"/>
+      <c r="AO15" s="28" t="n"/>
+      <c r="AP15" s="28" t="n"/>
+      <c r="AQ15" s="28" t="n"/>
+      <c r="AR15" s="28" t="n"/>
+      <c r="AS15" s="28" t="n"/>
+      <c r="AT15" s="28" t="n"/>
+      <c r="AU15" s="28" t="n"/>
+      <c r="AV15" s="28" t="n"/>
+      <c r="AW15" s="28" t="n"/>
+      <c r="AX15" s="28" t="n"/>
+      <c r="AY15" s="28" t="n"/>
+      <c r="AZ15" s="28" t="n"/>
+      <c r="BA15" s="28" t="n"/>
+      <c r="BB15" s="28" t="n"/>
+      <c r="BC15" s="28" t="n"/>
+      <c r="BD15" s="28" t="n"/>
+      <c r="BE15" s="28" t="n"/>
+      <c r="BF15" s="29" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="29" t="n"/>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>配送時間帯</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="n"/>
+      <c r="E16" s="28" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+      <c r="H16" s="28" t="n"/>
+      <c r="I16" s="29" t="n"/>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>deliveryTimeKbn</t>
+        </is>
+      </c>
+      <c r="K16" s="28" t="n"/>
+      <c r="L16" s="28" t="n"/>
+      <c r="M16" s="28" t="n"/>
+      <c r="N16" s="28" t="n"/>
+      <c r="O16" s="28" t="n"/>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="29" t="n"/>
+      <c r="R16" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S16" s="28" t="n"/>
+      <c r="T16" s="28" t="n"/>
+      <c r="U16" s="28" t="n"/>
+      <c r="V16" s="29" t="n"/>
+      <c r="W16" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X16" s="28" t="n"/>
+      <c r="Y16" s="28" t="n"/>
+      <c r="Z16" s="28" t="n"/>
+      <c r="AA16" s="29" t="n"/>
+      <c r="AB16" s="14" t="inlineStr"/>
+      <c r="AC16" s="28" t="n"/>
+      <c r="AD16" s="28" t="n"/>
+      <c r="AE16" s="28" t="n"/>
+      <c r="AF16" s="28" t="n"/>
+      <c r="AG16" s="28" t="n"/>
+      <c r="AH16" s="28" t="n"/>
+      <c r="AI16" s="28" t="n"/>
+      <c r="AJ16" s="28" t="n"/>
+      <c r="AK16" s="28" t="n"/>
+      <c r="AL16" s="28" t="n"/>
+      <c r="AM16" s="28" t="n"/>
+      <c r="AN16" s="28" t="n"/>
+      <c r="AO16" s="28" t="n"/>
+      <c r="AP16" s="28" t="n"/>
+      <c r="AQ16" s="28" t="n"/>
+      <c r="AR16" s="28" t="n"/>
+      <c r="AS16" s="28" t="n"/>
+      <c r="AT16" s="28" t="n"/>
+      <c r="AU16" s="28" t="n"/>
+      <c r="AV16" s="28" t="n"/>
+      <c r="AW16" s="28" t="n"/>
+      <c r="AX16" s="28" t="n"/>
+      <c r="AY16" s="28" t="n"/>
+      <c r="AZ16" s="28" t="n"/>
+      <c r="BA16" s="28" t="n"/>
+      <c r="BB16" s="28" t="n"/>
+      <c r="BC16" s="28" t="n"/>
+      <c r="BD16" s="28" t="n"/>
+      <c r="BE16" s="28" t="n"/>
+      <c r="BF16" s="29" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B17" s="29" t="n"/>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="29" t="n"/>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>remarks</t>
+        </is>
+      </c>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="28" t="n"/>
+      <c r="M17" s="28" t="n"/>
+      <c r="N17" s="28" t="n"/>
+      <c r="O17" s="28" t="n"/>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="29" t="n"/>
+      <c r="R17" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S17" s="28" t="n"/>
+      <c r="T17" s="28" t="n"/>
+      <c r="U17" s="28" t="n"/>
+      <c r="V17" s="29" t="n"/>
+      <c r="W17" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X17" s="28" t="n"/>
+      <c r="Y17" s="28" t="n"/>
+      <c r="Z17" s="28" t="n"/>
+      <c r="AA17" s="29" t="n"/>
+      <c r="AB17" s="14" t="inlineStr"/>
+      <c r="AC17" s="28" t="n"/>
+      <c r="AD17" s="28" t="n"/>
+      <c r="AE17" s="28" t="n"/>
+      <c r="AF17" s="28" t="n"/>
+      <c r="AG17" s="28" t="n"/>
+      <c r="AH17" s="28" t="n"/>
+      <c r="AI17" s="28" t="n"/>
+      <c r="AJ17" s="28" t="n"/>
+      <c r="AK17" s="28" t="n"/>
+      <c r="AL17" s="28" t="n"/>
+      <c r="AM17" s="28" t="n"/>
+      <c r="AN17" s="28" t="n"/>
+      <c r="AO17" s="28" t="n"/>
+      <c r="AP17" s="28" t="n"/>
+      <c r="AQ17" s="28" t="n"/>
+      <c r="AR17" s="28" t="n"/>
+      <c r="AS17" s="28" t="n"/>
+      <c r="AT17" s="28" t="n"/>
+      <c r="AU17" s="28" t="n"/>
+      <c r="AV17" s="28" t="n"/>
+      <c r="AW17" s="28" t="n"/>
+      <c r="AX17" s="28" t="n"/>
+      <c r="AY17" s="28" t="n"/>
+      <c r="AZ17" s="28" t="n"/>
+      <c r="BA17" s="28" t="n"/>
+      <c r="BB17" s="28" t="n"/>
+      <c r="BC17" s="28" t="n"/>
+      <c r="BD17" s="28" t="n"/>
+      <c r="BE17" s="28" t="n"/>
+      <c r="BF17" s="29" t="n"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B18" s="29" t="n"/>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>受注明細</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="n"/>
+      <c r="E18" s="28" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+      <c r="H18" s="28" t="n"/>
+      <c r="I18" s="29" t="n"/>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>detailList</t>
+        </is>
+      </c>
+      <c r="K18" s="28" t="n"/>
+      <c r="L18" s="28" t="n"/>
+      <c r="M18" s="28" t="n"/>
+      <c r="N18" s="28" t="n"/>
+      <c r="O18" s="28" t="n"/>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="29" t="n"/>
+      <c r="R18" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S18" s="28" t="n"/>
+      <c r="T18" s="28" t="n"/>
+      <c r="U18" s="28" t="n"/>
+      <c r="V18" s="29" t="n"/>
+      <c r="W18" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X18" s="28" t="n"/>
+      <c r="Y18" s="28" t="n"/>
+      <c r="Z18" s="28" t="n"/>
+      <c r="AA18" s="29" t="n"/>
+      <c r="AB18" s="14" t="inlineStr"/>
+      <c r="AC18" s="28" t="n"/>
+      <c r="AD18" s="28" t="n"/>
+      <c r="AE18" s="28" t="n"/>
+      <c r="AF18" s="28" t="n"/>
+      <c r="AG18" s="28" t="n"/>
+      <c r="AH18" s="28" t="n"/>
+      <c r="AI18" s="28" t="n"/>
+      <c r="AJ18" s="28" t="n"/>
+      <c r="AK18" s="28" t="n"/>
+      <c r="AL18" s="28" t="n"/>
+      <c r="AM18" s="28" t="n"/>
+      <c r="AN18" s="28" t="n"/>
+      <c r="AO18" s="28" t="n"/>
+      <c r="AP18" s="28" t="n"/>
+      <c r="AQ18" s="28" t="n"/>
+      <c r="AR18" s="28" t="n"/>
+      <c r="AS18" s="28" t="n"/>
+      <c r="AT18" s="28" t="n"/>
+      <c r="AU18" s="28" t="n"/>
+      <c r="AV18" s="28" t="n"/>
+      <c r="AW18" s="28" t="n"/>
+      <c r="AX18" s="28" t="n"/>
+      <c r="AY18" s="28" t="n"/>
+      <c r="AZ18" s="28" t="n"/>
+      <c r="BA18" s="28" t="n"/>
+      <c r="BB18" s="28" t="n"/>
+      <c r="BC18" s="28" t="n"/>
+      <c r="BD18" s="28" t="n"/>
+      <c r="BE18" s="28" t="n"/>
+      <c r="BF18" s="29" t="n"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B19" s="29" t="n"/>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>明細番号</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="n"/>
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+      <c r="H19" s="28" t="n"/>
+      <c r="I19" s="29" t="n"/>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>detail.lineNo</t>
+        </is>
+      </c>
+      <c r="K19" s="28" t="n"/>
+      <c r="L19" s="28" t="n"/>
+      <c r="M19" s="28" t="n"/>
+      <c r="N19" s="28" t="n"/>
+      <c r="O19" s="28" t="n"/>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="29" t="n"/>
+      <c r="R19" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S19" s="28" t="n"/>
+      <c r="T19" s="28" t="n"/>
+      <c r="U19" s="28" t="n"/>
+      <c r="V19" s="29" t="n"/>
+      <c r="W19" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X19" s="28" t="n"/>
+      <c r="Y19" s="28" t="n"/>
+      <c r="Z19" s="28" t="n"/>
+      <c r="AA19" s="29" t="n"/>
+      <c r="AB19" s="14" t="inlineStr"/>
+      <c r="AC19" s="28" t="n"/>
+      <c r="AD19" s="28" t="n"/>
+      <c r="AE19" s="28" t="n"/>
+      <c r="AF19" s="28" t="n"/>
+      <c r="AG19" s="28" t="n"/>
+      <c r="AH19" s="28" t="n"/>
+      <c r="AI19" s="28" t="n"/>
+      <c r="AJ19" s="28" t="n"/>
+      <c r="AK19" s="28" t="n"/>
+      <c r="AL19" s="28" t="n"/>
+      <c r="AM19" s="28" t="n"/>
+      <c r="AN19" s="28" t="n"/>
+      <c r="AO19" s="28" t="n"/>
+      <c r="AP19" s="28" t="n"/>
+      <c r="AQ19" s="28" t="n"/>
+      <c r="AR19" s="28" t="n"/>
+      <c r="AS19" s="28" t="n"/>
+      <c r="AT19" s="28" t="n"/>
+      <c r="AU19" s="28" t="n"/>
+      <c r="AV19" s="28" t="n"/>
+      <c r="AW19" s="28" t="n"/>
+      <c r="AX19" s="28" t="n"/>
+      <c r="AY19" s="28" t="n"/>
+      <c r="AZ19" s="28" t="n"/>
+      <c r="BA19" s="28" t="n"/>
+      <c r="BB19" s="28" t="n"/>
+      <c r="BC19" s="28" t="n"/>
+      <c r="BD19" s="28" t="n"/>
+      <c r="BE19" s="28" t="n"/>
+      <c r="BF19" s="29" t="n"/>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B20" s="29" t="n"/>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>商品コード</t>
+        </is>
+      </c>
+      <c r="D20" s="28" t="n"/>
+      <c r="E20" s="28" t="n"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+      <c r="H20" s="28" t="n"/>
+      <c r="I20" s="29" t="n"/>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>detail.productCd</t>
+        </is>
+      </c>
+      <c r="K20" s="28" t="n"/>
+      <c r="L20" s="28" t="n"/>
+      <c r="M20" s="28" t="n"/>
+      <c r="N20" s="28" t="n"/>
+      <c r="O20" s="28" t="n"/>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="29" t="n"/>
+      <c r="R20" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S20" s="28" t="n"/>
+      <c r="T20" s="28" t="n"/>
+      <c r="U20" s="28" t="n"/>
+      <c r="V20" s="29" t="n"/>
+      <c r="W20" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X20" s="28" t="n"/>
+      <c r="Y20" s="28" t="n"/>
+      <c r="Z20" s="28" t="n"/>
+      <c r="AA20" s="29" t="n"/>
+      <c r="AB20" s="14" t="inlineStr"/>
+      <c r="AC20" s="28" t="n"/>
+      <c r="AD20" s="28" t="n"/>
+      <c r="AE20" s="28" t="n"/>
+      <c r="AF20" s="28" t="n"/>
+      <c r="AG20" s="28" t="n"/>
+      <c r="AH20" s="28" t="n"/>
+      <c r="AI20" s="28" t="n"/>
+      <c r="AJ20" s="28" t="n"/>
+      <c r="AK20" s="28" t="n"/>
+      <c r="AL20" s="28" t="n"/>
+      <c r="AM20" s="28" t="n"/>
+      <c r="AN20" s="28" t="n"/>
+      <c r="AO20" s="28" t="n"/>
+      <c r="AP20" s="28" t="n"/>
+      <c r="AQ20" s="28" t="n"/>
+      <c r="AR20" s="28" t="n"/>
+      <c r="AS20" s="28" t="n"/>
+      <c r="AT20" s="28" t="n"/>
+      <c r="AU20" s="28" t="n"/>
+      <c r="AV20" s="28" t="n"/>
+      <c r="AW20" s="28" t="n"/>
+      <c r="AX20" s="28" t="n"/>
+      <c r="AY20" s="28" t="n"/>
+      <c r="AZ20" s="28" t="n"/>
+      <c r="BA20" s="28" t="n"/>
+      <c r="BB20" s="28" t="n"/>
+      <c r="BC20" s="28" t="n"/>
+      <c r="BD20" s="28" t="n"/>
+      <c r="BE20" s="28" t="n"/>
+      <c r="BF20" s="29" t="n"/>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B21" s="29" t="n"/>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>商品名</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="n"/>
+      <c r="E21" s="28" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+      <c r="H21" s="28" t="n"/>
+      <c r="I21" s="29" t="n"/>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>detail.productName</t>
+        </is>
+      </c>
+      <c r="K21" s="28" t="n"/>
+      <c r="L21" s="28" t="n"/>
+      <c r="M21" s="28" t="n"/>
+      <c r="N21" s="28" t="n"/>
+      <c r="O21" s="28" t="n"/>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="29" t="n"/>
+      <c r="R21" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S21" s="28" t="n"/>
+      <c r="T21" s="28" t="n"/>
+      <c r="U21" s="28" t="n"/>
+      <c r="V21" s="29" t="n"/>
+      <c r="W21" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X21" s="28" t="n"/>
+      <c r="Y21" s="28" t="n"/>
+      <c r="Z21" s="28" t="n"/>
+      <c r="AA21" s="29" t="n"/>
+      <c r="AB21" s="14" t="inlineStr"/>
+      <c r="AC21" s="28" t="n"/>
+      <c r="AD21" s="28" t="n"/>
+      <c r="AE21" s="28" t="n"/>
+      <c r="AF21" s="28" t="n"/>
+      <c r="AG21" s="28" t="n"/>
+      <c r="AH21" s="28" t="n"/>
+      <c r="AI21" s="28" t="n"/>
+      <c r="AJ21" s="28" t="n"/>
+      <c r="AK21" s="28" t="n"/>
+      <c r="AL21" s="28" t="n"/>
+      <c r="AM21" s="28" t="n"/>
+      <c r="AN21" s="28" t="n"/>
+      <c r="AO21" s="28" t="n"/>
+      <c r="AP21" s="28" t="n"/>
+      <c r="AQ21" s="28" t="n"/>
+      <c r="AR21" s="28" t="n"/>
+      <c r="AS21" s="28" t="n"/>
+      <c r="AT21" s="28" t="n"/>
+      <c r="AU21" s="28" t="n"/>
+      <c r="AV21" s="28" t="n"/>
+      <c r="AW21" s="28" t="n"/>
+      <c r="AX21" s="28" t="n"/>
+      <c r="AY21" s="28" t="n"/>
+      <c r="AZ21" s="28" t="n"/>
+      <c r="BA21" s="28" t="n"/>
+      <c r="BB21" s="28" t="n"/>
+      <c r="BC21" s="28" t="n"/>
+      <c r="BD21" s="28" t="n"/>
+      <c r="BE21" s="28" t="n"/>
+      <c r="BF21" s="29" t="n"/>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B22" s="29" t="n"/>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>単価</t>
+        </is>
+      </c>
+      <c r="D22" s="28" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+      <c r="H22" s="28" t="n"/>
+      <c r="I22" s="29" t="n"/>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>detail.unitPrice</t>
+        </is>
+      </c>
+      <c r="K22" s="28" t="n"/>
+      <c r="L22" s="28" t="n"/>
+      <c r="M22" s="28" t="n"/>
+      <c r="N22" s="28" t="n"/>
+      <c r="O22" s="28" t="n"/>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="29" t="n"/>
+      <c r="R22" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S22" s="28" t="n"/>
+      <c r="T22" s="28" t="n"/>
+      <c r="U22" s="28" t="n"/>
+      <c r="V22" s="29" t="n"/>
+      <c r="W22" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X22" s="28" t="n"/>
+      <c r="Y22" s="28" t="n"/>
+      <c r="Z22" s="28" t="n"/>
+      <c r="AA22" s="29" t="n"/>
+      <c r="AB22" s="14" t="inlineStr"/>
+      <c r="AC22" s="28" t="n"/>
+      <c r="AD22" s="28" t="n"/>
+      <c r="AE22" s="28" t="n"/>
+      <c r="AF22" s="28" t="n"/>
+      <c r="AG22" s="28" t="n"/>
+      <c r="AH22" s="28" t="n"/>
+      <c r="AI22" s="28" t="n"/>
+      <c r="AJ22" s="28" t="n"/>
+      <c r="AK22" s="28" t="n"/>
+      <c r="AL22" s="28" t="n"/>
+      <c r="AM22" s="28" t="n"/>
+      <c r="AN22" s="28" t="n"/>
+      <c r="AO22" s="28" t="n"/>
+      <c r="AP22" s="28" t="n"/>
+      <c r="AQ22" s="28" t="n"/>
+      <c r="AR22" s="28" t="n"/>
+      <c r="AS22" s="28" t="n"/>
+      <c r="AT22" s="28" t="n"/>
+      <c r="AU22" s="28" t="n"/>
+      <c r="AV22" s="28" t="n"/>
+      <c r="AW22" s="28" t="n"/>
+      <c r="AX22" s="28" t="n"/>
+      <c r="AY22" s="28" t="n"/>
+      <c r="AZ22" s="28" t="n"/>
+      <c r="BA22" s="28" t="n"/>
+      <c r="BB22" s="28" t="n"/>
+      <c r="BC22" s="28" t="n"/>
+      <c r="BD22" s="28" t="n"/>
+      <c r="BE22" s="28" t="n"/>
+      <c r="BF22" s="29" t="n"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B23" s="29" t="n"/>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="D23" s="28" t="n"/>
+      <c r="E23" s="28" t="n"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+      <c r="H23" s="28" t="n"/>
+      <c r="I23" s="29" t="n"/>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>detail.quantity</t>
+        </is>
+      </c>
+      <c r="K23" s="28" t="n"/>
+      <c r="L23" s="28" t="n"/>
+      <c r="M23" s="28" t="n"/>
+      <c r="N23" s="28" t="n"/>
+      <c r="O23" s="28" t="n"/>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="29" t="n"/>
+      <c r="R23" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S23" s="28" t="n"/>
+      <c r="T23" s="28" t="n"/>
+      <c r="U23" s="28" t="n"/>
+      <c r="V23" s="29" t="n"/>
+      <c r="W23" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X23" s="28" t="n"/>
+      <c r="Y23" s="28" t="n"/>
+      <c r="Z23" s="28" t="n"/>
+      <c r="AA23" s="29" t="n"/>
+      <c r="AB23" s="14" t="inlineStr"/>
+      <c r="AC23" s="28" t="n"/>
+      <c r="AD23" s="28" t="n"/>
+      <c r="AE23" s="28" t="n"/>
+      <c r="AF23" s="28" t="n"/>
+      <c r="AG23" s="28" t="n"/>
+      <c r="AH23" s="28" t="n"/>
+      <c r="AI23" s="28" t="n"/>
+      <c r="AJ23" s="28" t="n"/>
+      <c r="AK23" s="28" t="n"/>
+      <c r="AL23" s="28" t="n"/>
+      <c r="AM23" s="28" t="n"/>
+      <c r="AN23" s="28" t="n"/>
+      <c r="AO23" s="28" t="n"/>
+      <c r="AP23" s="28" t="n"/>
+      <c r="AQ23" s="28" t="n"/>
+      <c r="AR23" s="28" t="n"/>
+      <c r="AS23" s="28" t="n"/>
+      <c r="AT23" s="28" t="n"/>
+      <c r="AU23" s="28" t="n"/>
+      <c r="AV23" s="28" t="n"/>
+      <c r="AW23" s="28" t="n"/>
+      <c r="AX23" s="28" t="n"/>
+      <c r="AY23" s="28" t="n"/>
+      <c r="AZ23" s="28" t="n"/>
+      <c r="BA23" s="28" t="n"/>
+      <c r="BB23" s="28" t="n"/>
+      <c r="BC23" s="28" t="n"/>
+      <c r="BD23" s="28" t="n"/>
+      <c r="BE23" s="28" t="n"/>
+      <c r="BF23" s="29" t="n"/>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B24" s="29" t="n"/>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>金額</t>
+        </is>
+      </c>
+      <c r="D24" s="28" t="n"/>
+      <c r="E24" s="28" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+      <c r="H24" s="28" t="n"/>
+      <c r="I24" s="29" t="n"/>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>detail.amount</t>
+        </is>
+      </c>
+      <c r="K24" s="28" t="n"/>
+      <c r="L24" s="28" t="n"/>
+      <c r="M24" s="28" t="n"/>
+      <c r="N24" s="28" t="n"/>
+      <c r="O24" s="28" t="n"/>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="29" t="n"/>
+      <c r="R24" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S24" s="28" t="n"/>
+      <c r="T24" s="28" t="n"/>
+      <c r="U24" s="28" t="n"/>
+      <c r="V24" s="29" t="n"/>
+      <c r="W24" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X24" s="28" t="n"/>
+      <c r="Y24" s="28" t="n"/>
+      <c r="Z24" s="28" t="n"/>
+      <c r="AA24" s="29" t="n"/>
+      <c r="AB24" s="14" t="inlineStr"/>
+      <c r="AC24" s="28" t="n"/>
+      <c r="AD24" s="28" t="n"/>
+      <c r="AE24" s="28" t="n"/>
+      <c r="AF24" s="28" t="n"/>
+      <c r="AG24" s="28" t="n"/>
+      <c r="AH24" s="28" t="n"/>
+      <c r="AI24" s="28" t="n"/>
+      <c r="AJ24" s="28" t="n"/>
+      <c r="AK24" s="28" t="n"/>
+      <c r="AL24" s="28" t="n"/>
+      <c r="AM24" s="28" t="n"/>
+      <c r="AN24" s="28" t="n"/>
+      <c r="AO24" s="28" t="n"/>
+      <c r="AP24" s="28" t="n"/>
+      <c r="AQ24" s="28" t="n"/>
+      <c r="AR24" s="28" t="n"/>
+      <c r="AS24" s="28" t="n"/>
+      <c r="AT24" s="28" t="n"/>
+      <c r="AU24" s="28" t="n"/>
+      <c r="AV24" s="28" t="n"/>
+      <c r="AW24" s="28" t="n"/>
+      <c r="AX24" s="28" t="n"/>
+      <c r="AY24" s="28" t="n"/>
+      <c r="AZ24" s="28" t="n"/>
+      <c r="BA24" s="28" t="n"/>
+      <c r="BB24" s="28" t="n"/>
+      <c r="BC24" s="28" t="n"/>
+      <c r="BD24" s="28" t="n"/>
+      <c r="BE24" s="28" t="n"/>
+      <c r="BF24" s="29" t="n"/>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B25" s="29" t="n"/>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>削除</t>
+        </is>
+      </c>
+      <c r="D25" s="28" t="n"/>
+      <c r="E25" s="28" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+      <c r="H25" s="28" t="n"/>
+      <c r="I25" s="29" t="n"/>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>detail.deleteChk</t>
+        </is>
+      </c>
+      <c r="K25" s="28" t="n"/>
+      <c r="L25" s="28" t="n"/>
+      <c r="M25" s="28" t="n"/>
+      <c r="N25" s="28" t="n"/>
+      <c r="O25" s="28" t="n"/>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="29" t="n"/>
+      <c r="R25" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S25" s="28" t="n"/>
+      <c r="T25" s="28" t="n"/>
+      <c r="U25" s="28" t="n"/>
+      <c r="V25" s="29" t="n"/>
+      <c r="W25" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X25" s="28" t="n"/>
+      <c r="Y25" s="28" t="n"/>
+      <c r="Z25" s="28" t="n"/>
+      <c r="AA25" s="29" t="n"/>
+      <c r="AB25" s="14" t="inlineStr"/>
+      <c r="AC25" s="28" t="n"/>
+      <c r="AD25" s="28" t="n"/>
+      <c r="AE25" s="28" t="n"/>
+      <c r="AF25" s="28" t="n"/>
+      <c r="AG25" s="28" t="n"/>
+      <c r="AH25" s="28" t="n"/>
+      <c r="AI25" s="28" t="n"/>
+      <c r="AJ25" s="28" t="n"/>
+      <c r="AK25" s="28" t="n"/>
+      <c r="AL25" s="28" t="n"/>
+      <c r="AM25" s="28" t="n"/>
+      <c r="AN25" s="28" t="n"/>
+      <c r="AO25" s="28" t="n"/>
+      <c r="AP25" s="28" t="n"/>
+      <c r="AQ25" s="28" t="n"/>
+      <c r="AR25" s="28" t="n"/>
+      <c r="AS25" s="28" t="n"/>
+      <c r="AT25" s="28" t="n"/>
+      <c r="AU25" s="28" t="n"/>
+      <c r="AV25" s="28" t="n"/>
+      <c r="AW25" s="28" t="n"/>
+      <c r="AX25" s="28" t="n"/>
+      <c r="AY25" s="28" t="n"/>
+      <c r="AZ25" s="28" t="n"/>
+      <c r="BA25" s="28" t="n"/>
+      <c r="BB25" s="28" t="n"/>
+      <c r="BC25" s="28" t="n"/>
+      <c r="BD25" s="28" t="n"/>
+      <c r="BE25" s="28" t="n"/>
+      <c r="BF25" s="29" t="n"/>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B26" s="29" t="n"/>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>行追加</t>
+        </is>
+      </c>
+      <c r="D26" s="28" t="n"/>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+      <c r="H26" s="28" t="n"/>
+      <c r="I26" s="29" t="n"/>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>btnAddRow</t>
+        </is>
+      </c>
+      <c r="K26" s="28" t="n"/>
+      <c r="L26" s="28" t="n"/>
+      <c r="M26" s="28" t="n"/>
+      <c r="N26" s="28" t="n"/>
+      <c r="O26" s="28" t="n"/>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="29" t="n"/>
+      <c r="R26" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S26" s="28" t="n"/>
+      <c r="T26" s="28" t="n"/>
+      <c r="U26" s="28" t="n"/>
+      <c r="V26" s="29" t="n"/>
+      <c r="W26" s="16" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="X26" s="28" t="n"/>
+      <c r="Y26" s="28" t="n"/>
+      <c r="Z26" s="28" t="n"/>
+      <c r="AA26" s="29" t="n"/>
+      <c r="AB26" s="14" t="inlineStr">
+        <is>
+          <t>明細は最大20行</t>
+        </is>
+      </c>
+      <c r="AC26" s="28" t="n"/>
+      <c r="AD26" s="28" t="n"/>
+      <c r="AE26" s="28" t="n"/>
+      <c r="AF26" s="28" t="n"/>
+      <c r="AG26" s="28" t="n"/>
+      <c r="AH26" s="28" t="n"/>
+      <c r="AI26" s="28" t="n"/>
+      <c r="AJ26" s="28" t="n"/>
+      <c r="AK26" s="28" t="n"/>
+      <c r="AL26" s="28" t="n"/>
+      <c r="AM26" s="28" t="n"/>
+      <c r="AN26" s="28" t="n"/>
+      <c r="AO26" s="28" t="n"/>
+      <c r="AP26" s="28" t="n"/>
+      <c r="AQ26" s="28" t="n"/>
+      <c r="AR26" s="28" t="n"/>
+      <c r="AS26" s="28" t="n"/>
+      <c r="AT26" s="28" t="n"/>
+      <c r="AU26" s="28" t="n"/>
+      <c r="AV26" s="28" t="n"/>
+      <c r="AW26" s="28" t="n"/>
+      <c r="AX26" s="28" t="n"/>
+      <c r="AY26" s="28" t="n"/>
+      <c r="AZ26" s="28" t="n"/>
+      <c r="BA26" s="28" t="n"/>
+      <c r="BB26" s="28" t="n"/>
+      <c r="BC26" s="28" t="n"/>
+      <c r="BD26" s="28" t="n"/>
+      <c r="BE26" s="28" t="n"/>
+      <c r="BF26" s="29" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>合計金額</t>
+        </is>
+      </c>
+      <c r="D27" s="28" t="n"/>
+      <c r="E27" s="28" t="n"/>
+      <c r="F27" s="28" t="n"/>
+      <c r="G27" s="28" t="n"/>
+      <c r="H27" s="28" t="n"/>
+      <c r="I27" s="29" t="n"/>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>totalAmount</t>
+        </is>
+      </c>
+      <c r="K27" s="28" t="n"/>
+      <c r="L27" s="28" t="n"/>
+      <c r="M27" s="28" t="n"/>
+      <c r="N27" s="28" t="n"/>
+      <c r="O27" s="28" t="n"/>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="29" t="n"/>
+      <c r="R27" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S27" s="28" t="n"/>
+      <c r="T27" s="28" t="n"/>
+      <c r="U27" s="28" t="n"/>
+      <c r="V27" s="29" t="n"/>
+      <c r="W27" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X27" s="28" t="n"/>
+      <c r="Y27" s="28" t="n"/>
+      <c r="Z27" s="28" t="n"/>
+      <c r="AA27" s="29" t="n"/>
+      <c r="AB27" s="14" t="inlineStr"/>
+      <c r="AC27" s="28" t="n"/>
+      <c r="AD27" s="28" t="n"/>
+      <c r="AE27" s="28" t="n"/>
+      <c r="AF27" s="28" t="n"/>
+      <c r="AG27" s="28" t="n"/>
+      <c r="AH27" s="28" t="n"/>
+      <c r="AI27" s="28" t="n"/>
+      <c r="AJ27" s="28" t="n"/>
+      <c r="AK27" s="28" t="n"/>
+      <c r="AL27" s="28" t="n"/>
+      <c r="AM27" s="28" t="n"/>
+      <c r="AN27" s="28" t="n"/>
+      <c r="AO27" s="28" t="n"/>
+      <c r="AP27" s="28" t="n"/>
+      <c r="AQ27" s="28" t="n"/>
+      <c r="AR27" s="28" t="n"/>
+      <c r="AS27" s="28" t="n"/>
+      <c r="AT27" s="28" t="n"/>
+      <c r="AU27" s="28" t="n"/>
+      <c r="AV27" s="28" t="n"/>
+      <c r="AW27" s="28" t="n"/>
+      <c r="AX27" s="28" t="n"/>
+      <c r="AY27" s="28" t="n"/>
+      <c r="AZ27" s="28" t="n"/>
+      <c r="BA27" s="28" t="n"/>
+      <c r="BB27" s="28" t="n"/>
+      <c r="BC27" s="28" t="n"/>
+      <c r="BD27" s="28" t="n"/>
+      <c r="BE27" s="28" t="n"/>
+      <c r="BF27" s="29" t="n"/>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B28" s="29" t="n"/>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>登録</t>
+        </is>
+      </c>
+      <c r="D28" s="28" t="n"/>
+      <c r="E28" s="28" t="n"/>
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="28" t="n"/>
+      <c r="H28" s="28" t="n"/>
+      <c r="I28" s="29" t="n"/>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>btnRegist</t>
+        </is>
+      </c>
+      <c r="K28" s="28" t="n"/>
+      <c r="L28" s="28" t="n"/>
+      <c r="M28" s="28" t="n"/>
+      <c r="N28" s="28" t="n"/>
+      <c r="O28" s="28" t="n"/>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="29" t="n"/>
+      <c r="R28" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S28" s="28" t="n"/>
+      <c r="T28" s="28" t="n"/>
+      <c r="U28" s="28" t="n"/>
+      <c r="V28" s="29" t="n"/>
+      <c r="W28" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X28" s="28" t="n"/>
+      <c r="Y28" s="28" t="n"/>
+      <c r="Z28" s="28" t="n"/>
+      <c r="AA28" s="29" t="n"/>
+      <c r="AB28" s="14" t="inlineStr"/>
+      <c r="AC28" s="28" t="n"/>
+      <c r="AD28" s="28" t="n"/>
+      <c r="AE28" s="28" t="n"/>
+      <c r="AF28" s="28" t="n"/>
+      <c r="AG28" s="28" t="n"/>
+      <c r="AH28" s="28" t="n"/>
+      <c r="AI28" s="28" t="n"/>
+      <c r="AJ28" s="28" t="n"/>
+      <c r="AK28" s="28" t="n"/>
+      <c r="AL28" s="28" t="n"/>
+      <c r="AM28" s="28" t="n"/>
+      <c r="AN28" s="28" t="n"/>
+      <c r="AO28" s="28" t="n"/>
+      <c r="AP28" s="28" t="n"/>
+      <c r="AQ28" s="28" t="n"/>
+      <c r="AR28" s="28" t="n"/>
+      <c r="AS28" s="28" t="n"/>
+      <c r="AT28" s="28" t="n"/>
+      <c r="AU28" s="28" t="n"/>
+      <c r="AV28" s="28" t="n"/>
+      <c r="AW28" s="28" t="n"/>
+      <c r="AX28" s="28" t="n"/>
+      <c r="AY28" s="28" t="n"/>
+      <c r="AZ28" s="28" t="n"/>
+      <c r="BA28" s="28" t="n"/>
+      <c r="BB28" s="28" t="n"/>
+      <c r="BC28" s="28" t="n"/>
+      <c r="BD28" s="28" t="n"/>
+      <c r="BE28" s="28" t="n"/>
+      <c r="BF28" s="29" t="n"/>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="B29" s="29" t="n"/>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>戻る</t>
+        </is>
+      </c>
+      <c r="D29" s="28" t="n"/>
+      <c r="E29" s="28" t="n"/>
+      <c r="F29" s="28" t="n"/>
+      <c r="G29" s="28" t="n"/>
+      <c r="H29" s="28" t="n"/>
+      <c r="I29" s="29" t="n"/>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>btnBack</t>
+        </is>
+      </c>
+      <c r="K29" s="28" t="n"/>
+      <c r="L29" s="28" t="n"/>
+      <c r="M29" s="28" t="n"/>
+      <c r="N29" s="28" t="n"/>
+      <c r="O29" s="28" t="n"/>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="29" t="n"/>
+      <c r="R29" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S29" s="28" t="n"/>
+      <c r="T29" s="28" t="n"/>
+      <c r="U29" s="28" t="n"/>
+      <c r="V29" s="29" t="n"/>
+      <c r="W29" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X29" s="28" t="n"/>
+      <c r="Y29" s="28" t="n"/>
+      <c r="Z29" s="28" t="n"/>
+      <c r="AA29" s="29" t="n"/>
+      <c r="AB29" s="14" t="inlineStr"/>
+      <c r="AC29" s="28" t="n"/>
+      <c r="AD29" s="28" t="n"/>
+      <c r="AE29" s="28" t="n"/>
+      <c r="AF29" s="28" t="n"/>
+      <c r="AG29" s="28" t="n"/>
+      <c r="AH29" s="28" t="n"/>
+      <c r="AI29" s="28" t="n"/>
+      <c r="AJ29" s="28" t="n"/>
+      <c r="AK29" s="28" t="n"/>
+      <c r="AL29" s="28" t="n"/>
+      <c r="AM29" s="28" t="n"/>
+      <c r="AN29" s="28" t="n"/>
+      <c r="AO29" s="28" t="n"/>
+      <c r="AP29" s="28" t="n"/>
+      <c r="AQ29" s="28" t="n"/>
+      <c r="AR29" s="28" t="n"/>
+      <c r="AS29" s="28" t="n"/>
+      <c r="AT29" s="28" t="n"/>
+      <c r="AU29" s="28" t="n"/>
+      <c r="AV29" s="28" t="n"/>
+      <c r="AW29" s="28" t="n"/>
+      <c r="AX29" s="28" t="n"/>
+      <c r="AY29" s="28" t="n"/>
+      <c r="AZ29" s="28" t="n"/>
+      <c r="BA29" s="28" t="n"/>
+      <c r="BB29" s="28" t="n"/>
+      <c r="BC29" s="28" t="n"/>
+      <c r="BD29" s="28" t="n"/>
+      <c r="BE29" s="28" t="n"/>
+      <c r="BF29" s="29" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="149">
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="W25:AA25"/>
+    <mergeCell ref="J14:Q14"/>
+    <mergeCell ref="J29:Q29"/>
+    <mergeCell ref="R10:V10"/>
+    <mergeCell ref="J13:Q13"/>
+    <mergeCell ref="C19:I19"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="R16:V16"/>
+    <mergeCell ref="AB19:BF19"/>
+    <mergeCell ref="R25:V25"/>
+    <mergeCell ref="J15:Q15"/>
+    <mergeCell ref="A4:BF4"/>
+    <mergeCell ref="AB28:BF28"/>
+    <mergeCell ref="J24:Q24"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="AI1:AL1"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="R20:V20"/>
+    <mergeCell ref="J26:Q26"/>
+    <mergeCell ref="W16:AA16"/>
+    <mergeCell ref="AB20:BF20"/>
+    <mergeCell ref="AB14:BF14"/>
+    <mergeCell ref="AB29:BF29"/>
+    <mergeCell ref="J16:Q16"/>
+    <mergeCell ref="AY2:BF2"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="R22:V22"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="W18:AA18"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="K6:AN6"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K5:AN5"/>
+    <mergeCell ref="R14:V14"/>
+    <mergeCell ref="AO5:AX5"/>
+    <mergeCell ref="J17:Q17"/>
+    <mergeCell ref="R23:V23"/>
+    <mergeCell ref="S2:X2"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="J19:Q19"/>
+    <mergeCell ref="J28:Q28"/>
+    <mergeCell ref="AO6:AX6"/>
+    <mergeCell ref="AB17:BF17"/>
+    <mergeCell ref="C18:I18"/>
+    <mergeCell ref="W20:AA20"/>
+    <mergeCell ref="AB10:BF10"/>
+    <mergeCell ref="W28:AA28"/>
+    <mergeCell ref="R27:V27"/>
+    <mergeCell ref="W22:AA22"/>
+    <mergeCell ref="AO7:AX7"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="AC2:AH2"/>
+    <mergeCell ref="W12:AA12"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="W21:AA21"/>
+    <mergeCell ref="C29:I29"/>
+    <mergeCell ref="R17:V17"/>
+    <mergeCell ref="A1:N2"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="AB22:BF22"/>
+    <mergeCell ref="J18:Q18"/>
+    <mergeCell ref="AB12:BF12"/>
+    <mergeCell ref="AB21:BF21"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="W10:AA10"/>
+    <mergeCell ref="R29:V29"/>
+    <mergeCell ref="R11:V11"/>
+    <mergeCell ref="O2:R2"/>
+    <mergeCell ref="J10:Q10"/>
+    <mergeCell ref="AB23:BF23"/>
+    <mergeCell ref="AI2:AL2"/>
+    <mergeCell ref="R13:V13"/>
+    <mergeCell ref="AB13:BF13"/>
+    <mergeCell ref="AU2:AX2"/>
+    <mergeCell ref="W26:AA26"/>
+    <mergeCell ref="S1:AH1"/>
+    <mergeCell ref="R15:V15"/>
+    <mergeCell ref="R24:V24"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="AB18:BF18"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="R21:V21"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="J20:Q20"/>
+    <mergeCell ref="R26:V26"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="K7:AN7"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="C16:I16"/>
+    <mergeCell ref="Y2:AB2"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="AY1:BF1"/>
+    <mergeCell ref="J22:Q22"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="J12:Q12"/>
+    <mergeCell ref="AB25:BF25"/>
+    <mergeCell ref="J21:Q21"/>
+    <mergeCell ref="W14:AA14"/>
+    <mergeCell ref="W29:AA29"/>
+    <mergeCell ref="W23:AA23"/>
+    <mergeCell ref="AB27:BF27"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="W13:AA13"/>
+    <mergeCell ref="J23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="AM2:AT2"/>
+    <mergeCell ref="AB11:BF11"/>
+    <mergeCell ref="W15:AA15"/>
+    <mergeCell ref="R19:V19"/>
+    <mergeCell ref="C5:J5"/>
+    <mergeCell ref="W24:AA24"/>
+    <mergeCell ref="R28:V28"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C15:I15"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="J27:Q27"/>
+    <mergeCell ref="AM1:AT1"/>
+    <mergeCell ref="AU1:AX1"/>
+    <mergeCell ref="R12:V12"/>
+    <mergeCell ref="AB15:BF15"/>
+    <mergeCell ref="AB24:BF24"/>
+    <mergeCell ref="J11:Q11"/>
+    <mergeCell ref="A9:BF9"/>
+    <mergeCell ref="J25:Q25"/>
+    <mergeCell ref="W27:AA27"/>
+    <mergeCell ref="AB26:BF26"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="W17:AA17"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="W11:AA11"/>
+    <mergeCell ref="AB16:BF16"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="W19:AA19"/>
+    <mergeCell ref="R18:V18"/>
+    <mergeCell ref="C27:I27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>